--- a/Test_Plan_MyApp.xlsx
+++ b/Test_Plan_MyApp.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="382">
   <si>
     <t>ID</t>
   </si>
@@ -2706,7 +2706,9 @@
       <c r="E11" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7">
@@ -2725,7 +2727,9 @@
       <c r="E12" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7">
@@ -2744,7 +2748,9 @@
       <c r="E13" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:7">
@@ -2763,7 +2769,9 @@
       <c r="E14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G14" s="16"/>
     </row>
     <row r="15" spans="1:7">
@@ -2782,7 +2790,9 @@
       <c r="E15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:7">
@@ -2801,7 +2811,9 @@
       <c r="E16" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7">
@@ -2820,7 +2832,9 @@
       <c r="E17" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7">
@@ -2839,7 +2853,9 @@
       <c r="E18" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7">
@@ -2858,7 +2874,9 @@
       <c r="E19" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7">
@@ -2877,7 +2895,9 @@
       <c r="E20" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="F20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7">
@@ -2896,7 +2916,9 @@
       <c r="E21" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="F21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:7">
@@ -2915,7 +2937,9 @@
       <c r="E22" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="F22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G22" s="16"/>
     </row>
     <row r="23" ht="25.5" spans="1:7">
@@ -2934,7 +2958,9 @@
       <c r="E23" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7">
@@ -2953,7 +2979,9 @@
       <c r="E24" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:7">
@@ -2972,7 +3000,9 @@
       <c r="E25" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7">
@@ -3012,7 +3042,9 @@
       <c r="E27" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="F27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G27" s="16"/>
     </row>
     <row r="28" spans="1:7">
@@ -3031,7 +3063,9 @@
       <c r="E28" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="F28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7">
@@ -3050,7 +3084,9 @@
       <c r="E29" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="3"/>
+      <c r="F29" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7">
@@ -3069,7 +3105,9 @@
       <c r="E30" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="F30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G30" s="16"/>
     </row>
     <row r="31" spans="1:7">
@@ -3088,7 +3126,9 @@
       <c r="E31" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="F31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G31" s="16"/>
     </row>
     <row r="32" spans="1:7">
@@ -3107,7 +3147,9 @@
       <c r="E32" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="F32" s="3"/>
+      <c r="F32" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G32" s="16"/>
     </row>
     <row r="33" spans="1:7">
@@ -3126,7 +3168,9 @@
       <c r="E33" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G33" s="16"/>
     </row>
     <row r="34" spans="1:7">
@@ -3145,7 +3189,9 @@
       <c r="E34" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F34" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G34" s="16"/>
     </row>
     <row r="35" spans="1:7">
@@ -3164,7 +3210,9 @@
       <c r="E35" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="F35" s="3"/>
+      <c r="F35" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:7">
@@ -3183,7 +3231,9 @@
       <c r="E36" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F36" s="3"/>
+      <c r="F36" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G36" s="16"/>
     </row>
     <row r="37" spans="1:7">
@@ -3202,7 +3252,9 @@
       <c r="E37" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="F37" s="3"/>
+      <c r="F37" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G37" s="16"/>
     </row>
     <row r="38" spans="1:7">
@@ -3221,7 +3273,9 @@
       <c r="E38" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="F38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G38" s="16"/>
     </row>
     <row r="39" spans="1:7">
@@ -3240,7 +3294,9 @@
       <c r="E39" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="F39" s="3"/>
+      <c r="F39" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G39" s="16"/>
     </row>
     <row r="40" spans="1:7">
@@ -3259,7 +3315,9 @@
       <c r="E40" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="F40" s="3"/>
+      <c r="F40" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G40" s="16"/>
     </row>
     <row r="41" spans="1:7">
@@ -3278,7 +3336,9 @@
       <c r="E41" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G41" s="16"/>
     </row>
     <row r="42" spans="1:7">
@@ -3297,7 +3357,9 @@
       <c r="E42" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="F42" s="3"/>
+      <c r="F42" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G42" s="16"/>
     </row>
     <row r="43" spans="1:7">
@@ -3316,7 +3378,9 @@
       <c r="E43" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="F43" s="3"/>
+      <c r="F43" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G43" s="16"/>
     </row>
     <row r="44" spans="1:7">
@@ -3335,7 +3399,9 @@
       <c r="E44" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="F44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G44" s="16"/>
     </row>
     <row r="45" spans="1:7">
@@ -3354,7 +3420,9 @@
       <c r="E45" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="F45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G45" s="16"/>
     </row>
     <row r="46" spans="1:7">
@@ -3373,7 +3441,9 @@
       <c r="E46" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="F46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G46" s="16"/>
     </row>
     <row r="47" spans="1:7">
@@ -3392,7 +3462,9 @@
       <c r="E47" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="F47" s="3"/>
+      <c r="F47" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G47" s="16"/>
     </row>
     <row r="48" spans="1:7">
@@ -3411,7 +3483,9 @@
       <c r="E48" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="F48" s="3"/>
+      <c r="F48" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G48" s="16"/>
     </row>
     <row r="49" spans="1:7">
@@ -3430,7 +3504,9 @@
       <c r="E49" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="F49" s="3"/>
+      <c r="F49" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G49" s="16"/>
     </row>
     <row r="50" spans="1:7">
@@ -3449,7 +3525,9 @@
       <c r="E50" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="F50" s="3"/>
+      <c r="F50" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G50" s="16"/>
     </row>
     <row r="51" spans="1:7">
@@ -3468,7 +3546,9 @@
       <c r="E51" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="F51" s="3"/>
+      <c r="F51" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G51" s="16"/>
     </row>
     <row r="52" spans="1:7">
@@ -3487,7 +3567,9 @@
       <c r="E52" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="F52" s="3"/>
+      <c r="F52" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G52" s="16"/>
     </row>
     <row r="53" spans="1:7">
@@ -3506,7 +3588,9 @@
       <c r="E53" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="F53" s="3"/>
+      <c r="F53" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G53" s="16"/>
     </row>
     <row r="54" spans="1:7">
@@ -3525,7 +3609,9 @@
       <c r="E54" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="F54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G54" s="16"/>
     </row>
     <row r="55" spans="1:7">
@@ -3544,7 +3630,9 @@
       <c r="E55" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="F55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G55" s="16"/>
     </row>
     <row r="56" spans="1:7">
@@ -3563,7 +3651,9 @@
       <c r="E56" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G56" s="16"/>
     </row>
     <row r="57" spans="1:7">
@@ -3582,7 +3672,9 @@
       <c r="E57" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="F57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G57" s="16"/>
     </row>
     <row r="58" spans="1:7">
@@ -3601,7 +3693,9 @@
       <c r="E58" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="F58" s="3"/>
+      <c r="F58" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G58" s="16"/>
     </row>
     <row r="59" spans="1:7">
@@ -3620,7 +3714,9 @@
       <c r="E59" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="F59" s="3"/>
+      <c r="F59" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G59" s="16"/>
     </row>
     <row r="60" spans="1:7">
@@ -3639,7 +3735,9 @@
       <c r="E60" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="F60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G60" s="16"/>
     </row>
     <row r="61" spans="1:7">
@@ -3658,7 +3756,9 @@
       <c r="E61" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="F61" s="3"/>
+      <c r="F61" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G61" s="16"/>
     </row>
     <row r="62" spans="1:7">
@@ -3677,7 +3777,9 @@
       <c r="E62" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="F62" s="3"/>
+      <c r="F62" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G62" s="16"/>
     </row>
     <row r="63" spans="1:7">
@@ -3696,7 +3798,9 @@
       <c r="E63" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="F63" s="3"/>
+      <c r="F63" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G63" s="16"/>
     </row>
     <row r="64" spans="1:7">
@@ -3715,7 +3819,9 @@
       <c r="E64" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="F64" s="3"/>
+      <c r="F64" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G64" s="16"/>
     </row>
     <row r="65" spans="1:7">
@@ -3886,7 +3992,9 @@
       <c r="E73" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="F73" s="3"/>
+      <c r="F73" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G73" s="16"/>
     </row>
     <row r="74" spans="1:7">
@@ -3943,7 +4051,9 @@
       <c r="E76" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="F76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G76" s="16"/>
     </row>
     <row r="77" spans="1:7">
@@ -3962,7 +4072,9 @@
       <c r="E77" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="F77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G77" s="16"/>
     </row>
     <row r="78" spans="1:7">
@@ -4019,7 +4131,9 @@
       <c r="E80" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G80" s="16"/>
     </row>
     <row r="81" spans="1:7">
@@ -4038,7 +4152,9 @@
       <c r="E81" s="16" t="s">
         <v>301</v>
       </c>
-      <c r="F81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G81" s="16"/>
     </row>
     <row r="82" spans="1:7">
@@ -4057,7 +4173,9 @@
       <c r="E82" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="F82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G82" s="16"/>
     </row>
     <row r="83" spans="1:7">
@@ -4076,7 +4194,9 @@
       <c r="E83" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G83" s="16"/>
     </row>
     <row r="84" spans="1:7">
@@ -4095,7 +4215,9 @@
       <c r="E84" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="F84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G84" s="16"/>
     </row>
     <row r="85" spans="1:7">
@@ -4114,7 +4236,9 @@
       <c r="E85" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="F85" s="3"/>
+      <c r="F85" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G85" s="16"/>
     </row>
     <row r="86" spans="1:7">
@@ -4133,7 +4257,9 @@
       <c r="E86" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="F86" s="3"/>
+      <c r="F86" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G86" s="16"/>
     </row>
     <row r="87" spans="1:7">
@@ -4152,7 +4278,9 @@
       <c r="E87" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="F87" s="3"/>
+      <c r="F87" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G87" s="16"/>
     </row>
     <row r="88" spans="1:7">
@@ -4171,7 +4299,9 @@
       <c r="E88" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="F88" s="3"/>
+      <c r="F88" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G88" s="16"/>
     </row>
     <row r="89" spans="1:7">
@@ -4190,7 +4320,9 @@
       <c r="E89" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="F89" s="3"/>
+      <c r="F89" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G89" s="16"/>
     </row>
     <row r="90" spans="1:7">
@@ -4209,7 +4341,9 @@
       <c r="E90" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="F90" s="3"/>
+      <c r="F90" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G90" s="16"/>
     </row>
     <row r="91" spans="1:7">
@@ -4228,7 +4362,9 @@
       <c r="E91" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="F91" s="3"/>
+      <c r="F91" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G91" s="16"/>
     </row>
     <row r="92" spans="1:7">
@@ -4247,7 +4383,9 @@
       <c r="E92" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="F92" s="3"/>
+      <c r="F92" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G92" s="16"/>
     </row>
     <row r="93" spans="1:7">
@@ -4266,7 +4404,9 @@
       <c r="E93" s="16" t="s">
         <v>344</v>
       </c>
-      <c r="F93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G93" s="16"/>
     </row>
     <row r="94" spans="1:7">
@@ -4285,7 +4425,9 @@
       <c r="E94" s="16" t="s">
         <v>348</v>
       </c>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G94" s="16"/>
     </row>
     <row r="95" spans="1:7">
@@ -4304,7 +4446,9 @@
       <c r="E95" s="16" t="s">
         <v>351</v>
       </c>
-      <c r="F95" s="3"/>
+      <c r="F95" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G95" s="16"/>
     </row>
     <row r="96" spans="1:7">
@@ -4323,7 +4467,9 @@
       <c r="E96" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="F96" s="3"/>
+      <c r="F96" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G96" s="16"/>
     </row>
     <row r="97" spans="1:7">
@@ -4342,7 +4488,9 @@
       <c r="E97" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="F97" s="3"/>
+      <c r="F97" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G97" s="16"/>
     </row>
     <row r="98" spans="1:7">
@@ -4361,7 +4509,9 @@
       <c r="E98" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="F98" s="3"/>
+      <c r="F98" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G98" s="16"/>
     </row>
     <row r="99" spans="1:7">
@@ -4380,7 +4530,9 @@
       <c r="E99" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="F99" s="3"/>
+      <c r="F99" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G99" s="16"/>
     </row>
     <row r="100" spans="1:7">
@@ -4399,7 +4551,9 @@
       <c r="E100" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="F100" s="3"/>
+      <c r="F100" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G100" s="16"/>
     </row>
     <row r="101" spans="1:7">
@@ -4418,7 +4572,9 @@
       <c r="E101" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="F101" s="3"/>
+      <c r="F101" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G101" s="16"/>
     </row>
     <row r="102" spans="1:7">
@@ -4437,7 +4593,9 @@
       <c r="E102" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="F102" s="3"/>
+      <c r="F102" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G102" s="16"/>
     </row>
   </sheetData>
@@ -4445,7 +4603,7 @@
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11:F102">
+    <dataValidation type="list" allowBlank="1" sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F42 F43 F44 F73 F76 F77 F27:F29 F30:F36 F37:F41 F45:F50 F51:F53 F54:F55 F56:F64 F65:F72 F74:F75 F78:F79 F80:F85 F86:F90 F91:F93 F94:F95 F96:F102">
       <formula1>"Chưa test,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Test_Plan_MyApp.xlsx
+++ b/Test_Plan_MyApp.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="382">
   <si>
     <t>ID</t>
   </si>
@@ -3840,7 +3840,9 @@
       <c r="E65" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="F65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G65" s="16"/>
     </row>
     <row r="66" spans="1:7">
@@ -3859,7 +3861,9 @@
       <c r="E66" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="F66" s="3"/>
+      <c r="F66" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G66" s="16"/>
     </row>
     <row r="67" spans="1:7">
@@ -3897,7 +3901,9 @@
       <c r="E68" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="F68" s="3"/>
+      <c r="F68" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G68" s="16"/>
     </row>
     <row r="69" spans="1:7">
@@ -3916,7 +3922,9 @@
       <c r="E69" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="F69" s="3"/>
+      <c r="F69" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G69" s="16"/>
     </row>
     <row r="70" spans="1:7">
@@ -3935,7 +3943,9 @@
       <c r="E70" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="F70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G70" s="16"/>
     </row>
     <row r="71" spans="1:7">
@@ -3954,7 +3964,9 @@
       <c r="E71" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="F71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G71" s="16"/>
     </row>
     <row r="72" spans="1:7">
@@ -3973,7 +3985,9 @@
       <c r="E72" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="F72" s="3"/>
+      <c r="F72" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G72" s="16"/>
     </row>
     <row r="73" spans="1:7">
@@ -4013,7 +4027,9 @@
       <c r="E74" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="F74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G74" s="16"/>
     </row>
     <row r="75" spans="1:7">
@@ -4032,7 +4048,9 @@
       <c r="E75" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="F75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G75" s="16"/>
     </row>
     <row r="76" spans="1:7">
@@ -4093,7 +4111,9 @@
       <c r="E78" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="F78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G78" s="16"/>
     </row>
     <row r="79" spans="1:7">
@@ -4112,7 +4132,9 @@
       <c r="E79" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="F79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="G79" s="16"/>
     </row>
     <row r="80" spans="1:7">
@@ -4603,7 +4625,7 @@
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="F2 F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23 F24 F25 F26 F42 F43 F44 F73 F76 F77 F27:F29 F30:F36 F37:F41 F45:F50 F51:F53 F54:F55 F56:F64 F65:F72 F74:F75 F78:F79 F80:F85 F86:F90 F91:F93 F94:F95 F96:F102">
+    <dataValidation type="list" allowBlank="1" sqref="F65 F66 F67 F68 F69 F72 F73 F74 F75 F78 F79 F2:F64 F70:F71 F76:F77 F80:F102">
       <formula1>"Chưa test,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
